--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseApplicationMainError.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseApplicationMainError.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <r>
       <rPr>
@@ -194,6 +192,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>错误信息</t>
+  </si>
+  <si>
     <t>{.index}</t>
   </si>
   <si>
@@ -222,6 +223,9 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -1175,9 +1179,10 @@
     <col min="8" max="8" width="18.125" customWidth="1"/>
     <col min="9" max="9" width="18.625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1208,37 +1213,43 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1246,28 +1257,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>